--- a/jogos_2024-10-30.xlsx
+++ b/jogos_2024-10-30.xlsx
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="AA3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>3.1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['61', '90+7']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45595.3125</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P4" t="n">
         <v>2.2</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.33</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AC4" t="n">
         <v>1.73</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AD4" t="n">
         <v>2</v>
       </c>
-      <c r="AA4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['61', '90+7']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45595.3125</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KF Gostivari</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,28 +1185,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
         <v>3.3</v>
@@ -1215,53 +1215,53 @@
         <v>1.29</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.36</v>
       </c>
-      <c r="X6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45595.375</v>
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Besa Dobërdoll</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>2.38</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['14', '23']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>5.5</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45595.375</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KF Gostivari</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Besa Dobërdoll</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.5</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['14', '23']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45595.375</v>
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Voska Sport</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.25</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
         <v>3.3</v>
@@ -1731,7 +1731,7 @@
         <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
         <v>1.36</v>
@@ -1740,44 +1740,44 @@
         <v>2.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['32', '79', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45595.375</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Voska Sport</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>6.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
         <v>3.3</v>
@@ -1860,7 +1860,7 @@
         <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
         <v>1.36</v>
@@ -1869,44 +1869,44 @@
         <v>2.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['32', '79', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.95</v>
       </c>
-      <c r="AD11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45595.375</v>
@@ -1923,26 +1923,26 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>4.36</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>7.78</v>
       </c>
       <c r="O12" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67', '84', '90+9']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['34', '53']</t>
+          <t>['26', '90+6']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45595.45833333334</v>
@@ -2052,119 +2052,119 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>3</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>3.25</v>
       </c>
       <c r="M13" t="n">
-        <v>4.36</v>
+        <v>2.88</v>
       </c>
       <c r="N13" t="n">
-        <v>7.78</v>
+        <v>2.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['67', '84', '90+9']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['26', '90+6']</t>
+          <t>['34', '45+4', '46']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
         <v>2.6</v>
       </c>
-      <c r="AI13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>3.75</v>
+        <v>1.73</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45595.45833333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,81 +2191,81 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="P14" t="n">
         <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC14" t="n">
         <v>2.2</v>
@@ -2275,25 +2275,25 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['34', '45+4', '46']</t>
+          <t>['34', '53']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45595.45833333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.5</v>
+        <v>2.17</v>
       </c>
       <c r="M20" t="n">
-        <v>2.88</v>
+        <v>3.61</v>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q20" t="n">
         <v>5</v>
       </c>
-      <c r="P20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.67</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.22</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>2.25</v>
+        <v>5.35</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.88</v>
+        <v>1.58</v>
       </c>
       <c r="Z20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['6', '25']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1.36</v>
       </c>
-      <c r="AA20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['52', '87']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45595.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.17</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.61</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.22</v>
       </c>
-      <c r="S21" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.67</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.57</v>
       </c>
       <c r="X21" t="n">
-        <v>5.35</v>
+        <v>2.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.58</v>
+        <v>2.88</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.38</v>
+        <v>1.36</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.21</v>
+        <v>6.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3183,20 +3183,20 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['6', '25']</t>
+          <t>['52', '87']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.15</v>
+        <v>1.68</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.36</v>
+        <v>2.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45595.58333333334</v>
@@ -3223,23 +3223,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Kings</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="M22" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="P22" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.33</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S22" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="T22" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="U22" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z22" t="n">
         <v>1.5</v>
       </c>
-      <c r="X22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AA22" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '72']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['77', '78']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.42</v>
+        <v>1.99</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.15</v>
+        <v>3.15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45595.60416666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>5.6</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.33</v>
+        <v>4.33</v>
       </c>
       <c r="R23" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V23" t="n">
         <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="X23" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['6', '72']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['77', '78']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.99</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.15</v>
+        <v>1.62</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.56</v>
+        <v>2.75</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45595.60416666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X24" t="n">
         <v>3</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="O24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.33</v>
-      </c>
       <c r="Y24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z24" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA24" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD24" t="n">
         <v>1.8</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['50', '67', '79']</t>
-        </is>
-      </c>
       <c r="AG24" t="n">
-        <v>2.9</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.75</v>
+        <v>1.62</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.3</v>
+        <v>2.75</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45595.60416666666</v>
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Real Kings</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SuperSport United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.5</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.48</v>
-      </c>
       <c r="X25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3699,20 +3699,20 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45595.60416666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Milan II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
       </c>
       <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
-        <v>3.23</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="X26" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.75</v>
+        <v>4.45</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['41', '56', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['19', '25']</t>
+          <t>['45+1', '73']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45595.60416666666</v>
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Clodiense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>FeralpiSalò</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="M28" t="n">
         <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>3.9</v>
+        <v>1.91</v>
       </c>
       <c r="O28" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA28" t="n">
         <v>4.33</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AB28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AI28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45595.60416666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SuperSport United</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>3.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>3.8</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="R29" t="n">
         <v>1.5</v>
       </c>
       <c r="S29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y29" t="n">
         <v>2.5</v>
       </c>
-      <c r="T29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z29" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD29" t="n">
         <v>1.67</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['26', '78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45595.60416666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Milan II</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1.95</v>
       </c>
-      <c r="M30" t="n">
+      <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['50', '67', '79']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>2.9</v>
       </c>
-      <c r="N30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T30" t="n">
+      <c r="AH30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI30" t="n">
         <v>3.75</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['45+1', '73']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>2.75</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45595.60416666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Clodiense</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FeralpiSalò</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
         <v>1</v>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.7</v>
+        <v>2.81</v>
       </c>
       <c r="M31" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X31" t="n">
         <v>3.2</v>
       </c>
-      <c r="N31" t="n">
+      <c r="Y31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.91</v>
       </c>
-      <c r="O31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['41', '56', '86']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['19', '25']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI31" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AJ31" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.62</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45595.60416666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,22 +4513,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4539,34 +4539,34 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O32" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
         <v>1.04</v>
@@ -4578,13 +4578,13 @@
         <v>2.75</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB32" t="n">
         <v>1.2</v>
@@ -4597,22 +4597,22 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['26', '78']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AJ32" t="n">
         <v>2.75</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="M35" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S35" t="n">
         <v>3.3</v>
       </c>
-      <c r="N35" t="n">
+      <c r="T35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD35" t="n">
         <v>2.45</v>
       </c>
-      <c r="O35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64', '81', '87']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '89']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45595.6875</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3</v>
       </c>
-      <c r="H36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="M36" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI36" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['64', '81', '87']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['19', '89']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45595.6875</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.57</v>
+        <v>3.18</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>5.18</v>
       </c>
       <c r="N37" t="n">
-        <v>2.19</v>
+        <v>1.66</v>
       </c>
       <c r="O37" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="T37" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.3</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['53', '77']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.4</v>
       </c>
-      <c r="X37" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
+      <c r="AH37" t="n">
         <v>1.55</v>
       </c>
-      <c r="AH37" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI37" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45595.6875</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="O38" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="P38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD38" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.42</v>
       </c>
-      <c r="S38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI38" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45595.6875</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.18</v>
+        <v>1.16</v>
       </c>
       <c r="M39" t="n">
-        <v>5.18</v>
+        <v>8.23</v>
       </c>
       <c r="N39" t="n">
-        <v>1.66</v>
+        <v>7.49</v>
       </c>
       <c r="O39" t="n">
-        <v>2.95</v>
+        <v>1.85</v>
       </c>
       <c r="P39" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X39" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['45+1', '65']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['20', '70']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI39" t="n">
         <v>1.4</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['53', '77']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AJ39" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45595.6875</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,109 +5545,109 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y40" t="n">
         <v>2</v>
       </c>
-      <c r="H40" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M40" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="N40" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="O40" t="n">
+      <c r="Z40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.85</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X40" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['45+1', '65']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['20', '70']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AI40" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45595.6875</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,16 +5674,16 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>2</v>
@@ -5692,36 +5692,36 @@
         <v>1</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1.48</v>
-      </c>
       <c r="M41" t="n">
-        <v>4.48</v>
+        <v>3.08</v>
       </c>
       <c r="N41" t="n">
-        <v>6.85</v>
+        <v>3.54</v>
       </c>
       <c r="O41" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="R41" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T41" t="n">
         <v>2.63</v>
@@ -5733,50 +5733,50 @@
         <v>1.04</v>
       </c>
       <c r="W41" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X41" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AC41" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['31', '49']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['3', '38']</t>
+          <t>['58', '63']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.85</v>
+        <v>1.93</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ41" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45595.69791666666</v>
@@ -5803,109 +5803,109 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="N42" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P42" t="n">
         <v>3</v>
       </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q42" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T42" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U42" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X42" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['30', '57', '90+3']</t>
+          <t>['60', '67']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.05</v>
+        <v>6.25</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.63</v>
+        <v>7</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45595.69791666666</v>
@@ -5932,109 +5932,109 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD43" t="n">
         <v>2</v>
       </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>2</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N43" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P43" t="n">
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI43" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q43" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X43" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC43" t="n">
+      <c r="AJ43" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>['58', '63']</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45595.69791666666</v>
@@ -6061,25 +6061,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5.12</v>
+        <v>1.54</v>
       </c>
       <c r="M44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y44" t="n">
         <v>1.7</v>
       </c>
-      <c r="N44" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="O44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Z44" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD44" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '57', '90+3']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45595.69791666666</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="M45" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="N45" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>7</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S45" t="n">
         <v>3</v>
       </c>
-      <c r="N45" t="n">
+      <c r="T45" t="n">
         <v>2.63</v>
       </c>
-      <c r="O45" t="n">
+      <c r="U45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA45" t="n">
         <v>3.2</v>
       </c>
-      <c r="P45" t="n">
+      <c r="AB45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC45" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W45" t="n">
+      <c r="AD45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['31', '49']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>['3', '38']</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AI45" t="n">
         <v>1.3</v>
       </c>
-      <c r="X45" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>['43', '60']</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ45" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45595.69791666666</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.38</v>
+        <v>1.39</v>
       </c>
       <c r="M46" t="n">
-        <v>1.69</v>
+        <v>5.1</v>
       </c>
       <c r="N46" t="n">
-        <v>4.48</v>
+        <v>7.83</v>
       </c>
       <c r="O46" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="P46" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S46" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V46" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X46" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AD46" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['70', '88']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['23', '74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45595.69791666666</v>
@@ -6448,22 +6448,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lucchese</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="O47" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="P47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y47" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q47" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.73</v>
-      </c>
       <c r="Z47" t="n">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['39', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45595.69791666666</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
         <v>2</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.13</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>7.67</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>10.02</v>
+        <v>2.63</v>
       </c>
       <c r="O48" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="P48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>15</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['43', '60']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>2.2</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X48" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>['60', '67']</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>7</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45595.69791666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,16 +6706,16 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lucchese</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N49" t="n">
+        <v>8</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z49" t="n">
         <v>1.7</v>
       </c>
-      <c r="M49" t="n">
+      <c r="AA49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AH49" t="n">
         <v>3.1</v>
       </c>
-      <c r="N49" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q49" t="n">
+      <c r="AI49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ49" t="n">
         <v>5.5</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45595.69791666666</v>
@@ -6835,16 +6835,16 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="M50" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="O50" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="P50" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="R50" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="S50" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="T50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>['39', '90+6']</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ50" t="n">
         <v>4</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>['16']</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45595.69791666666</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,22 +6964,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q51" t="n">
         <v>4.33</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P51" t="n">
+      <c r="R51" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y51" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Z51" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC51" t="n">
         <v>2.2</v>
       </c>
-      <c r="R51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD51" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>['86', '87']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI51" t="n">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45595.69791666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,19 +7093,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.33</v>
+        <v>4.33</v>
       </c>
       <c r="M52" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>1.67</v>
       </c>
       <c r="O52" t="n">
-        <v>1.83</v>
+        <v>4.33</v>
       </c>
       <c r="P52" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q52" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q52" t="n">
-        <v>8.5</v>
-      </c>
       <c r="R52" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S52" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T52" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.6</v>
+        <v>2.31</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86', '87']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="AJ52" t="n">
-        <v>5.5</v>
+        <v>1.44</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45595.69791666666</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
         <v>2</v>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.39</v>
+        <v>3.38</v>
       </c>
       <c r="M53" t="n">
-        <v>5.1</v>
+        <v>1.69</v>
       </c>
       <c r="N53" t="n">
-        <v>7.83</v>
+        <v>4.48</v>
       </c>
       <c r="O53" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="P53" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="R53" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S53" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="T53" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U53" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V53" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W53" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="X53" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="Z53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>['23', '74']</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ53" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>['70', '88']</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>4.33</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45595.69791666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>6</v>
+        <v>3.44</v>
       </c>
       <c r="M54" t="n">
-        <v>3.8</v>
+        <v>4.14</v>
       </c>
       <c r="N54" t="n">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="O54" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="P54" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U54" t="n">
         <v>1.44</v>
       </c>
-      <c r="S54" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V54" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W54" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X54" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="Y54" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD54" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z54" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['35', '49', '69']</t>
+          <t>['31', '74']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['22', '80']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45595.70833333334</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,25 +7480,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G55" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" t="n">
         <v>2</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.44</v>
+        <v>6</v>
       </c>
       <c r="M55" t="n">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="N55" t="n">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="O55" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="P55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC55" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R55" t="n">
+      <c r="AD55" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>['35', '49', '69']</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>['22', '80']</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ55" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X55" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>['31', '74']</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45595.70833333334</v>
